--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="144">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T08:42:19+00:00</t>
+    <t>2026-07-09T18:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,35 +263,29 @@
     <t>Identifiant unique affecté à l'archive de portabilité</t>
   </si>
   <si>
-    <t>pdlgc-manifest.extractTime</t>
+    <t>pdlgc-manifest.exportType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Type de l'export : UNITAIRE|CIBLE|MASSIF</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/pdlgc-export-type-vs|0.1.0</t>
+  </si>
+  <si>
+    <t>pdlgc-manifest.exportStartTime</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
-    <t>Date et heure de l'extraction</t>
-  </si>
-  <si>
-    <t>pdlgc-manifest.exportType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Type de l'export : UNITAIRE|CIBLE|MASSIF</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/pdlgc-export-type-vs|0.1.0</t>
-  </si>
-  <si>
-    <t>pdlgc-manifest.exportStartTime</t>
-  </si>
-  <si>
     <t>Date de début de la période couverte par l'export dans le cas d'un export ciblé</t>
   </si>
   <si>
@@ -323,7 +317,7 @@
     <t>pdlgc-manifest.editeurSortant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-editeur-sortant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/pdlgc-fournisseur-sortant
 </t>
   </si>
   <si>
@@ -769,7 +763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.80078125" customWidth="true" bestFit="true"/>
@@ -782,7 +776,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="66.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.9140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1180,13 +1174,11 @@
         <v>73</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y4" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="Y4" s="2"/>
       <c r="Z4" t="s" s="2">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>73</v>
@@ -1221,10 +1213,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1232,7 +1224,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>79</v>
@@ -1247,13 +1239,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1280,11 +1272,13 @@
         <v>73</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y5" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z5" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>73</v>
@@ -1302,10 +1296,10 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>79</v>
@@ -1345,7 +1339,7 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>91</v>
@@ -1430,7 +1424,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>79</v>
@@ -1478,13 +1472,11 @@
         <v>73</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y7" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="Y7" s="2"/>
       <c r="Z7" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AA7" t="s" s="2">
         <v>73</v>
@@ -1505,7 +1497,7 @@
         <v>92</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>79</v>
@@ -1519,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1530,7 +1522,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>79</v>
@@ -1545,13 +1537,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1578,11 +1570,13 @@
         <v>73</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y8" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z8" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>73</v>
@@ -1600,10 +1594,10 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>79</v>
@@ -1617,10 +1611,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1628,7 +1622,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>79</v>
@@ -1643,13 +1637,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1700,10 +1694,10 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>79</v>
@@ -1717,10 +1711,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1743,13 +1737,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1800,7 +1794,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -1817,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1843,7 +1837,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>105</v>
@@ -1900,7 +1894,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -1931,7 +1925,7 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1943,13 +1937,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2006,21 +2000,21 @@
         <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>73</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2028,10 +2022,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2043,13 +2037,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2100,38 +2094,38 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2143,15 +2137,17 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>73</v>
@@ -2188,43 +2184,43 @@
         <v>73</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>73</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2237,24 +2233,26 @@
         <v>73</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>73</v>
       </c>
@@ -2290,19 +2288,19 @@
         <v>73</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2314,51 +2312,47 @@
         <v>73</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>73</v>
       </c>
@@ -2406,27 +2400,27 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>126</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2449,7 +2443,7 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>136</v>
@@ -2482,13 +2476,11 @@
         <v>73</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>73</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2506,7 +2498,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2534,7 +2526,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2549,7 +2541,7 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>138</v>
@@ -2582,11 +2574,13 @@
         <v>73</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>73</v>
@@ -2607,7 +2601,7 @@
         <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2632,7 +2626,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2647,13 +2641,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2707,7 +2701,7 @@
         <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2721,10 +2715,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2747,7 +2741,7 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>143</v>
@@ -2804,7 +2798,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2816,106 +2810,6 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K21" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:12:06+00:00</t>
+    <t>2026-07-09T18:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T18:19:16+00:00</t>
+    <t>2026-07-15T06:27:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T06:27:44+00:00</t>
+    <t>2026-07-15T13:41:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T13:41:49+00:00</t>
+    <t>2026-07-15T16:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:11:54+00:00</t>
+    <t>2026-07-16T08:21:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:21:58+00:00</t>
+    <t>2026-07-16T08:46:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:46:36+00:00</t>
+    <t>2026-07-16T10:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T10:52:32+00:00</t>
+    <t>2026-07-16T11:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T11:12:17+00:00</t>
+    <t>2026-07-16T21:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T21:31:30+00:00</t>
+    <t>2026-07-17T08:00:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T08:00:04+00:00</t>
+    <t>2026-07-17T11:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T11:25:46+00:00</t>
+    <t>2026-07-17T14:49:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T14:49:58+00:00</t>
+    <t>2026-07-19T17:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/pdlgc-export-type-vs|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/vs-pdlgc-export-type|0.1.0</t>
   </si>
   <si>
     <t>pdlgc-manifest.exportStartTime</t>
@@ -301,7 +301,7 @@
     <t>COMPLETE|PARTIAL|SAMPLE</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/pdlgc-repo-type-vs|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/vs-pdlgc-export-status|0.1.0</t>
   </si>
   <si>
     <t>pdlgc-manifest.comments</t>
@@ -324,7 +324,7 @@
     <t>Editeur responsable de l'export des données LGC</t>
   </si>
   <si>
-    <t>pdlgc-manifest.PatientArchiveCount</t>
+    <t>pdlgc-manifest.patientArchiveCount</t>
   </si>
   <si>
     <t xml:space="preserve">positiveInt
@@ -334,7 +334,7 @@
     <t>Nombre d'archives patients transportées</t>
   </si>
   <si>
-    <t>pdlgc-manifest.TransverseArchiveCount</t>
+    <t>pdlgc-manifest.transverseArchiveCount</t>
   </si>
   <si>
     <t>Nombre d'archives transverse trasnportées</t>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>Patient | Transverse</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/ValueSet/vs-pdlgc-archive-type|0.1.0</t>
   </si>
   <si>
     <t>pdlgc-manifest.Archive.patientId</t>
@@ -791,13 +794,13 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.99609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.3125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.4375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.08984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2480,7 +2483,7 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2515,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2544,10 +2547,10 @@
         <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2598,7 +2601,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2615,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2641,13 +2644,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2698,7 +2701,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -2715,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2744,10 +2747,10 @@
         <v>96</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2798,7 +2801,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>

--- a/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
+++ b/spec-tech/ig/StructureDefinition-pdlgc-manifest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
